--- a/Check.xlsx
+++ b/Check.xlsx
@@ -19,7 +19,7 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="179">
   <si>
     <t>Чек-лист ручного тестирования мобильного приложения "В Хосписе"
-Устройство Samsung Galaxy S20FE, модель SM-G780G/DSM, ОС Android 13, API 30</t>
+Устройство Samsung Galaxy S20FE, модель SM-G780G/DSM, ОС Android 13, API 36</t>
   </si>
   <si>
     <t>Группа проверок/модуль</t>

--- a/Check.xlsx
+++ b/Check.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="CMoG3Fqwil+JD/P/XdQDRLaFncViNk6A2N8uSGBvUng="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="MX2LeUB6u8azSmZUHYgsgmN7HJcIcXEwm44AMVV9nLM="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="175">
   <si>
     <t>Чек-лист ручного тестирования мобильного приложения "В Хосписе"
 Устройство Samsung Galaxy S20FE, модель SM-G780G/DSM, ОС Android 13, API 36</t>
@@ -115,9 +115,6 @@
     <t>2.2 Переход с главной страницы приложения в раздел "Новости" через главное меню</t>
   </si>
   <si>
-    <t>2.3 Переход в раздле "О приложении" через главное меню</t>
-  </si>
-  <si>
     <t>2.4 Переход на главную страницу приложения через главное меню</t>
   </si>
   <si>
@@ -154,28 +151,19 @@
     <t>4.3 Переход в раздел "Новости" через главное меню</t>
   </si>
   <si>
-    <t>4.4 Переход в раздел "О приложении" через главное меню</t>
+    <t>5.1 Возможность перехода между страницами приложения</t>
   </si>
   <si>
     <t>5. Страница "Новости"</t>
   </si>
   <si>
-    <t>5.1 Возможность перехода между страницами приложения</t>
-  </si>
-  <si>
     <t>5.1.1 Переход на главную страницу приложения через главное меню</t>
   </si>
   <si>
-    <t>5.1.2 Переход на страницу "О приложении" через главное меню</t>
-  </si>
-  <si>
-    <t>ссылка на страницу не активна</t>
-  </si>
-  <si>
-    <t>5.1.3 Переход на страницу "Цитаты" через кнопку на панели управления приложения</t>
-  </si>
-  <si>
-    <t>5.1.4 Переход на страницу "Новости" через главное меню</t>
+    <t>5.1.2 Переход на страницу "Цитаты" через кнопку на панели управления приложения</t>
+  </si>
+  <si>
+    <t>5.1.3 Переход на страницу "Новости" через главное меню</t>
   </si>
   <si>
     <t>ссылка не должна быть активна</t>
@@ -196,12 +184,12 @@
     <t>5.2.4 Работа кнопки "Редактирование"</t>
   </si>
   <si>
+    <t>6.1 Оставить все поля пустыми</t>
+  </si>
+  <si>
     <t>6. Вкладка "Фильтровать новости" на странице "Новости"</t>
   </si>
   <si>
-    <t>6.1 Оставить все поля пустыми</t>
-  </si>
-  <si>
     <t>6.2 Выбор категории "Объявления" из выпадающего списка</t>
   </si>
   <si>
@@ -262,12 +250,12 @@
     <t>6.19 Работа кнопки "Отмена"</t>
   </si>
   <si>
+    <t>7.1 Создание новостей</t>
+  </si>
+  <si>
     <t xml:space="preserve">7. Вкладка "Панель управления" </t>
   </si>
   <si>
-    <t>7.1 Создание новостей</t>
-  </si>
-  <si>
     <t>7.1.1 Создание активной новости с категорией "День рождения"</t>
   </si>
   <si>
@@ -442,12 +430,12 @@
     <t>7.3.19 Работа кнопки "Отмена"</t>
   </si>
   <si>
+    <t>8.1 Потребление энергии, памяти</t>
+  </si>
+  <si>
     <t>8. Характеристики устройства</t>
   </si>
   <si>
-    <t>8.1 Потребление энергии, памяти</t>
-  </si>
-  <si>
     <t>8.1.1 Расход заряда батареи</t>
   </si>
   <si>
@@ -526,12 +514,12 @@
     <t>8.3.9 Работа кнопок/активность всех областей экрана при наличии защитного экрана</t>
   </si>
   <si>
+    <t>9.1 Поведение приложения при подключении к сети 4G</t>
+  </si>
+  <si>
     <t>9. Сетевые характеристики</t>
   </si>
   <si>
-    <t>9.1 Поведение приложения при подключении к сети 4G</t>
-  </si>
-  <si>
     <t>9.2 Поведение приложения при подключении к сети 3G</t>
   </si>
   <si>
@@ -550,10 +538,10 @@
     <t>9.7 Поведение приложения при возобновлении подлючения к сети</t>
   </si>
   <si>
+    <t>10.1 Соответствие приложения гайдлайнам магазинов приложений (AppStore, GooglePlay и др.)</t>
+  </si>
+  <si>
     <t>10. Характеристики приложения</t>
-  </si>
-  <si>
-    <t>10.1 Соответствие приложения гайдлайнам магазинов приложений (AppStore, GooglePlay и др.)</t>
   </si>
 </sst>
 </file>
@@ -617,7 +605,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="51">
+  <borders count="52">
     <border/>
     <border>
       <left style="medium">
@@ -902,6 +890,57 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
     </border>
     <border>
       <left/>
@@ -920,13 +959,10 @@
       <bottom/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <bottom style="thin">
+      <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
     </border>
@@ -934,6 +970,25 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -942,9 +997,30 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -953,89 +1029,9 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-    </border>
-    <border>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -1094,7 +1090,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="101">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1202,65 +1198,78 @@
     </xf>
     <xf borderId="25" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="26" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="15" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="15" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="27" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="27" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="28" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="29" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="18" fillId="0" fontId="5" numFmtId="14" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="28" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="30" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="31" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="29" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="30" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="32" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="30" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="31" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="32" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="18" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="15" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="19" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="21" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="22" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="33" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="34" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="35" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="28" fillId="0" fontId="5" numFmtId="14" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="30" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="36" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="30" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="30" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="30" fillId="0" fontId="5" numFmtId="17" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="32" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="31" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="33" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="37" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="34" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="3" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="35" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="36" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="37" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="38" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="38" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="39" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="40" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="39" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="41" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="13" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1269,7 +1278,7 @@
     <xf borderId="13" fillId="0" fontId="5" numFmtId="17" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="32" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="31" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="15" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1284,15 +1293,15 @@
     <xf borderId="14" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="40" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="41" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="32" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="42" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="43" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="31" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="38" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="40" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="42" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="44" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="13" fillId="0" fontId="5" numFmtId="16" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -1302,37 +1311,36 @@
     <xf borderId="30" fillId="0" fontId="5" numFmtId="14" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="43" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="13" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="14" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="44" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="45" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="46" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="21" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="47" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="45" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="48" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="46" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="47" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="48" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="49" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="50" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="50" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="51" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="16" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="7" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1871,109 +1879,109 @@
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="20"/>
-      <c r="B25" s="30" t="s">
+      <c r="B25" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="22" t="s">
+      <c r="C25" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="33"/>
+      <c r="F25" s="34"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="10"/>
+      <c r="B26" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="D25" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" s="23"/>
-      <c r="F25" s="24"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="20"/>
-      <c r="B26" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="C26" s="32" t="s">
+      <c r="D26" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" s="27"/>
+      <c r="F26" s="28"/>
+    </row>
+    <row r="27" ht="38.25" customHeight="1">
+      <c r="A27" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D26" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" s="33"/>
-      <c r="F26" s="34"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="10"/>
-      <c r="B27" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="C27" s="26" t="s">
+      <c r="D27" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" s="18"/>
+      <c r="F27" s="37" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="20"/>
+      <c r="B28" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="E28" s="23"/>
+      <c r="F28" s="39" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="10"/>
+      <c r="B29" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="E27" s="27"/>
-      <c r="F27" s="28"/>
-    </row>
-    <row r="28" ht="38.25" customHeight="1">
-      <c r="A28" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="C28" s="17" t="s">
+      <c r="D29" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" s="27"/>
+      <c r="F29" s="28"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D28" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="E28" s="18"/>
-      <c r="F28" s="37" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="20"/>
-      <c r="B29" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="C29" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="D29" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="E29" s="23"/>
-      <c r="F29" s="39" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="10"/>
-      <c r="B30" s="35" t="s">
-        <v>40</v>
-      </c>
-      <c r="C30" s="26" t="s">
+      <c r="D30" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" s="18"/>
+      <c r="F30" s="19"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="20"/>
+      <c r="B31" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="D30" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" s="27"/>
-      <c r="F30" s="28"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="29" t="s">
-        <v>42</v>
-      </c>
-      <c r="C31" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D31" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="E31" s="18"/>
-      <c r="F31" s="19"/>
+      <c r="D31" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" s="23"/>
+      <c r="F31" s="24"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="20"/>
@@ -1990,1299 +1998,1303 @@
       <c r="F32" s="24"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="20"/>
-      <c r="B33" s="30" t="s">
+      <c r="A33" s="10"/>
+      <c r="B33" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="C33" s="22" t="s">
+      <c r="C33" s="41"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="42"/>
+    </row>
+    <row r="34" ht="12.75" customHeight="1">
+      <c r="A34" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="44" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="D33" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="E33" s="23"/>
-      <c r="F33" s="24"/>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="10"/>
-      <c r="B34" s="35" t="s">
-        <v>45</v>
-      </c>
-      <c r="C34" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="D34" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" s="27"/>
-      <c r="F34" s="28"/>
-    </row>
-    <row r="35" ht="12.75" customHeight="1">
-      <c r="A35" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="B35" s="40" t="s">
+      <c r="D34" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" s="46"/>
+      <c r="F34" s="47"/>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="48"/>
+      <c r="B35" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="C35" s="41"/>
-      <c r="D35" s="41"/>
-      <c r="E35" s="41"/>
-      <c r="F35" s="42"/>
+      <c r="C35" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" s="23"/>
+      <c r="F35" s="50"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="20"/>
-      <c r="B36" s="30" t="s">
+      <c r="A36" s="48"/>
+      <c r="B36" s="51" t="s">
         <v>48</v>
       </c>
-      <c r="C36" s="22" t="s">
+      <c r="C36" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="D36" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="E36" s="23"/>
-      <c r="F36" s="24"/>
+      <c r="D36" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E36" s="33"/>
+      <c r="F36" s="53" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="20"/>
-      <c r="B37" s="30" t="s">
-        <v>49</v>
-      </c>
-      <c r="C37" s="22" t="s">
+      <c r="A37" s="48"/>
+      <c r="B37" s="54" t="s">
+        <v>50</v>
+      </c>
+      <c r="C37" s="55"/>
+      <c r="D37" s="55"/>
+      <c r="E37" s="55"/>
+      <c r="F37" s="56"/>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="48"/>
+      <c r="B38" s="57" t="s">
+        <v>51</v>
+      </c>
+      <c r="C38" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="D37" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="E37" s="23"/>
-      <c r="F37" s="43" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="20"/>
-      <c r="B38" s="30" t="s">
-        <v>51</v>
-      </c>
-      <c r="C38" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="D38" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="E38" s="23"/>
-      <c r="F38" s="43"/>
+      <c r="D38" s="58"/>
+      <c r="E38" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" s="47"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="20"/>
+      <c r="A39" s="48"/>
       <c r="B39" s="30" t="s">
         <v>52</v>
       </c>
       <c r="C39" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="D39" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="E39" s="23"/>
-      <c r="F39" s="44" t="s">
+      <c r="D39" s="38"/>
+      <c r="E39" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F39" s="24"/>
+    </row>
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="A40" s="48"/>
+      <c r="B40" s="30" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="20"/>
-      <c r="B40" s="45" t="s">
+      <c r="C40" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D40" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" s="23"/>
+      <c r="F40" s="24"/>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="48"/>
+      <c r="B41" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="C40" s="46"/>
-      <c r="D40" s="46"/>
-      <c r="E40" s="46"/>
-      <c r="F40" s="47"/>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="20"/>
-      <c r="B41" s="48" t="s">
+      <c r="C41" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D41" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" s="27"/>
+      <c r="F41" s="28"/>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="59"/>
+      <c r="B42" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="C41" s="22" t="s">
+      <c r="C42" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="D41" s="38"/>
-      <c r="E41" s="23" t="s">
+      <c r="D42" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" s="18"/>
+      <c r="F42" s="19"/>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B43" s="60" t="s">
+        <v>57</v>
+      </c>
+      <c r="C43" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="D43" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" s="46"/>
+      <c r="F43" s="47"/>
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="20"/>
+      <c r="B44" s="60" t="s">
+        <v>58</v>
+      </c>
+      <c r="C44" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="F41" s="24"/>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="20"/>
-      <c r="B42" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="C42" s="22" t="s">
+      <c r="F44" s="47"/>
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="20"/>
+      <c r="B45" s="60" t="s">
+        <v>59</v>
+      </c>
+      <c r="C45" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="D42" s="38"/>
-      <c r="E42" s="23" t="s">
+      <c r="D45" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="F42" s="24"/>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="20"/>
-      <c r="B43" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="C43" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="D43" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="E43" s="23"/>
-      <c r="F43" s="24"/>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="10"/>
-      <c r="B44" s="35" t="s">
-        <v>58</v>
-      </c>
-      <c r="C44" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="D44" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="E44" s="27"/>
-      <c r="F44" s="28"/>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="B45" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="C45" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="D45" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="E45" s="18"/>
-      <c r="F45" s="19"/>
+      <c r="F45" s="47"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="20"/>
-      <c r="B46" s="49" t="s">
-        <v>61</v>
-      </c>
-      <c r="C46" s="50" t="s">
+      <c r="B46" s="60" t="s">
+        <v>60</v>
+      </c>
+      <c r="C46" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="D46" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E46" s="51"/>
-      <c r="F46" s="52"/>
+      <c r="D46" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46" s="47"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="20"/>
-      <c r="B47" s="49" t="s">
-        <v>62</v>
-      </c>
-      <c r="C47" s="50" t="s">
+      <c r="B47" s="60" t="s">
+        <v>61</v>
+      </c>
+      <c r="C47" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="D47" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E47" s="51" t="s">
+      <c r="D47" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="F47" s="52"/>
+      <c r="F47" s="47"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="20"/>
-      <c r="B48" s="49" t="s">
-        <v>63</v>
-      </c>
-      <c r="C48" s="50" t="s">
+      <c r="B48" s="60" t="s">
+        <v>62</v>
+      </c>
+      <c r="C48" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="D48" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E48" s="51" t="s">
+      <c r="D48" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="F48" s="52"/>
+      <c r="F48" s="47"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="20"/>
-      <c r="B49" s="49" t="s">
-        <v>64</v>
-      </c>
-      <c r="C49" s="50" t="s">
+      <c r="B49" s="60" t="s">
+        <v>63</v>
+      </c>
+      <c r="C49" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="D49" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E49" s="51" t="s">
+      <c r="D49" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="F49" s="52"/>
+      <c r="F49" s="47"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="20"/>
-      <c r="B50" s="49" t="s">
-        <v>65</v>
-      </c>
-      <c r="C50" s="50" t="s">
+      <c r="B50" s="60" t="s">
+        <v>64</v>
+      </c>
+      <c r="C50" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="D50" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E50" s="51" t="s">
+      <c r="D50" s="61" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="F50" s="52"/>
+      <c r="F50" s="47"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="20"/>
-      <c r="B51" s="49" t="s">
-        <v>66</v>
-      </c>
-      <c r="C51" s="50" t="s">
+      <c r="B51" s="60" t="s">
+        <v>65</v>
+      </c>
+      <c r="C51" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="D51" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E51" s="51" t="s">
-        <v>12</v>
-      </c>
-      <c r="F51" s="52"/>
+      <c r="D51" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" s="46"/>
+      <c r="F51" s="47"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="20"/>
-      <c r="B52" s="49" t="s">
-        <v>67</v>
-      </c>
-      <c r="C52" s="50" t="s">
+      <c r="B52" s="60" t="s">
+        <v>66</v>
+      </c>
+      <c r="C52" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="D52" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E52" s="51" t="s">
-        <v>12</v>
-      </c>
-      <c r="F52" s="52"/>
+      <c r="D52" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="E52" s="46"/>
+      <c r="F52" s="47"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="20"/>
-      <c r="B53" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="C53" s="50" t="s">
+      <c r="B53" s="60" t="s">
+        <v>67</v>
+      </c>
+      <c r="C53" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="D53" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="E53" s="51" t="s">
-        <v>12</v>
-      </c>
-      <c r="F53" s="52"/>
+      <c r="D53" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="E53" s="46"/>
+      <c r="F53" s="47"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="20"/>
-      <c r="B54" s="49" t="s">
-        <v>69</v>
-      </c>
-      <c r="C54" s="50" t="s">
+      <c r="B54" s="60" t="s">
+        <v>68</v>
+      </c>
+      <c r="C54" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="D54" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E54" s="51"/>
-      <c r="F54" s="52"/>
+      <c r="D54" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="E54" s="46"/>
+      <c r="F54" s="47"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="20"/>
-      <c r="B55" s="49" t="s">
-        <v>70</v>
-      </c>
-      <c r="C55" s="50" t="s">
+      <c r="B55" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="C55" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="D55" s="54" t="s">
-        <v>37</v>
-      </c>
-      <c r="E55" s="51"/>
-      <c r="F55" s="52"/>
+      <c r="D55" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="E55" s="46"/>
+      <c r="F55" s="47"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="20"/>
-      <c r="B56" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="C56" s="50" t="s">
+      <c r="B56" s="60" t="s">
+        <v>70</v>
+      </c>
+      <c r="C56" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="D56" s="54" t="s">
-        <v>37</v>
-      </c>
-      <c r="E56" s="51"/>
-      <c r="F56" s="52"/>
+      <c r="D56" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" s="46"/>
+      <c r="F56" s="47"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="20"/>
-      <c r="B57" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="C57" s="50" t="s">
+      <c r="B57" s="62" t="s">
+        <v>71</v>
+      </c>
+      <c r="C57" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="D57" s="54" t="s">
-        <v>37</v>
-      </c>
-      <c r="E57" s="51"/>
-      <c r="F57" s="52"/>
+      <c r="D57" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E57" s="46"/>
+      <c r="F57" s="47"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="20"/>
-      <c r="B58" s="49" t="s">
+      <c r="B58" s="60" t="s">
+        <v>72</v>
+      </c>
+      <c r="C58" s="45" t="s">
+        <v>25</v>
+      </c>
+      <c r="D58" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="E58" s="46"/>
+      <c r="F58" s="63" t="s">
         <v>73</v>
       </c>
-      <c r="C58" s="50" t="s">
-        <v>10</v>
-      </c>
-      <c r="D58" s="54" t="s">
-        <v>37</v>
-      </c>
-      <c r="E58" s="51"/>
-      <c r="F58" s="52"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="20"/>
-      <c r="B59" s="49" t="s">
+      <c r="B59" s="60" t="s">
         <v>74</v>
       </c>
-      <c r="C59" s="50" t="s">
-        <v>10</v>
-      </c>
-      <c r="D59" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E59" s="51"/>
-      <c r="F59" s="52"/>
+      <c r="C59" s="45" t="s">
+        <v>25</v>
+      </c>
+      <c r="D59" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="E59" s="46"/>
+      <c r="F59" s="63" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="20"/>
-      <c r="B60" s="55" t="s">
-        <v>75</v>
-      </c>
-      <c r="C60" s="50" t="s">
+      <c r="B60" s="64" t="s">
+        <v>76</v>
+      </c>
+      <c r="C60" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="D60" s="66" t="s">
+        <v>11</v>
+      </c>
+      <c r="E60" s="66"/>
+      <c r="F60" s="67"/>
+    </row>
+    <row r="61" ht="15.75" customHeight="1">
+      <c r="A61" s="10"/>
+      <c r="B61" s="68" t="s">
+        <v>77</v>
+      </c>
+      <c r="C61" s="69"/>
+      <c r="D61" s="69"/>
+      <c r="E61" s="69"/>
+      <c r="F61" s="70"/>
+    </row>
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="43" t="s">
+        <v>78</v>
+      </c>
+      <c r="B62" s="60" t="s">
+        <v>79</v>
+      </c>
+      <c r="C62" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="D60" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E60" s="51"/>
-      <c r="F60" s="52"/>
-    </row>
-    <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="20"/>
-      <c r="B61" s="49" t="s">
-        <v>76</v>
-      </c>
-      <c r="C61" s="50" t="s">
+      <c r="D62" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E62" s="46"/>
+      <c r="F62" s="47"/>
+    </row>
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="A63" s="48"/>
+      <c r="B63" s="71" t="s">
+        <v>80</v>
+      </c>
+      <c r="C63" s="72" t="s">
+        <v>10</v>
+      </c>
+      <c r="D63" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="E63" s="46"/>
+      <c r="F63" s="63" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="A64" s="48"/>
+      <c r="B64" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C64" s="73" t="s">
+        <v>10</v>
+      </c>
+      <c r="D64" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E64" s="46"/>
+      <c r="F64" s="47"/>
+    </row>
+    <row r="65" ht="15.75" customHeight="1">
+      <c r="A65" s="48"/>
+      <c r="B65" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="C65" s="73" t="s">
+        <v>10</v>
+      </c>
+      <c r="D65" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E65" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F65" s="47"/>
+    </row>
+    <row r="66" ht="15.75" customHeight="1">
+      <c r="A66" s="48"/>
+      <c r="B66" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="C66" s="73" t="s">
+        <v>10</v>
+      </c>
+      <c r="D66" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E66" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F66" s="47"/>
+    </row>
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="A67" s="48"/>
+      <c r="B67" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="C67" s="73" t="s">
+        <v>10</v>
+      </c>
+      <c r="D67" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E67" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F67" s="47"/>
+    </row>
+    <row r="68" ht="15.75" customHeight="1">
+      <c r="A68" s="48"/>
+      <c r="B68" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="C68" s="73" t="s">
+        <v>10</v>
+      </c>
+      <c r="D68" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E68" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F68" s="47"/>
+    </row>
+    <row r="69" ht="15.75" customHeight="1">
+      <c r="A69" s="48"/>
+      <c r="B69" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="C69" s="73" t="s">
+        <v>10</v>
+      </c>
+      <c r="D69" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E69" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F69" s="47"/>
+    </row>
+    <row r="70" ht="15.75" customHeight="1">
+      <c r="A70" s="48"/>
+      <c r="B70" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="C70" s="73" t="s">
+        <v>10</v>
+      </c>
+      <c r="D70" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E70" s="46"/>
+      <c r="F70" s="47"/>
+    </row>
+    <row r="71" ht="15.75" customHeight="1">
+      <c r="A71" s="48"/>
+      <c r="B71" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="C71" s="73" t="s">
+        <v>10</v>
+      </c>
+      <c r="D71" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E71" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F71" s="47"/>
+    </row>
+    <row r="72" ht="15.75" customHeight="1">
+      <c r="A72" s="48"/>
+      <c r="B72" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C72" s="73" t="s">
+        <v>10</v>
+      </c>
+      <c r="D72" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E72" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F72" s="47"/>
+    </row>
+    <row r="73" ht="15.75" customHeight="1">
+      <c r="A73" s="48"/>
+      <c r="B73" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="C73" s="73" t="s">
+        <v>10</v>
+      </c>
+      <c r="D73" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E73" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F73" s="47"/>
+    </row>
+    <row r="74" ht="15.75" customHeight="1">
+      <c r="A74" s="48"/>
+      <c r="B74" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="C74" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="D61" s="54" t="s">
-        <v>37</v>
-      </c>
-      <c r="E61" s="51"/>
-      <c r="F61" s="56" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="20"/>
-      <c r="B62" s="49" t="s">
-        <v>78</v>
-      </c>
-      <c r="C62" s="50" t="s">
+      <c r="D74" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E74" s="46"/>
+      <c r="F74" s="47"/>
+    </row>
+    <row r="75" ht="15.75" customHeight="1">
+      <c r="A75" s="48"/>
+      <c r="B75" s="74" t="s">
+        <v>93</v>
+      </c>
+      <c r="C75" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="D62" s="54" t="s">
-        <v>37</v>
-      </c>
-      <c r="E62" s="51"/>
-      <c r="F62" s="56" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="10"/>
-      <c r="B63" s="57" t="s">
-        <v>80</v>
-      </c>
-      <c r="C63" s="58" t="s">
+      <c r="D75" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E75" s="46"/>
+      <c r="F75" s="47"/>
+    </row>
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="A76" s="48"/>
+      <c r="B76" s="74" t="s">
+        <v>94</v>
+      </c>
+      <c r="C76" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="D63" s="59" t="s">
-        <v>11</v>
-      </c>
-      <c r="E63" s="59"/>
-      <c r="F63" s="60"/>
-    </row>
-    <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="61" t="s">
-        <v>81</v>
-      </c>
-      <c r="B64" s="62" t="s">
-        <v>82</v>
-      </c>
-      <c r="C64" s="63"/>
-      <c r="D64" s="63"/>
-      <c r="E64" s="63"/>
-      <c r="F64" s="64"/>
-    </row>
-    <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="65"/>
-      <c r="B65" s="49" t="s">
-        <v>83</v>
-      </c>
-      <c r="C65" s="50" t="s">
+      <c r="D76" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="E76" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F76" s="47"/>
+    </row>
+    <row r="77" ht="15.75" customHeight="1">
+      <c r="A77" s="48"/>
+      <c r="B77" s="74" t="s">
+        <v>95</v>
+      </c>
+      <c r="C77" s="73" t="s">
+        <v>25</v>
+      </c>
+      <c r="D77" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="E77" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F77" s="47"/>
+    </row>
+    <row r="78" ht="15.75" customHeight="1">
+      <c r="A78" s="48"/>
+      <c r="B78" s="74" t="s">
+        <v>96</v>
+      </c>
+      <c r="C78" s="73" t="s">
+        <v>25</v>
+      </c>
+      <c r="D78" s="61" t="s">
+        <v>11</v>
+      </c>
+      <c r="E78" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F78" s="47"/>
+    </row>
+    <row r="79" ht="15.75" customHeight="1">
+      <c r="A79" s="48"/>
+      <c r="B79" s="74" t="s">
+        <v>97</v>
+      </c>
+      <c r="C79" s="73" t="s">
+        <v>25</v>
+      </c>
+      <c r="D79" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E79" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F79" s="75"/>
+    </row>
+    <row r="80" ht="15.75" customHeight="1">
+      <c r="A80" s="48"/>
+      <c r="B80" s="74" t="s">
+        <v>98</v>
+      </c>
+      <c r="C80" s="73" t="s">
+        <v>25</v>
+      </c>
+      <c r="D80" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="E80" s="46"/>
+      <c r="F80" s="75"/>
+    </row>
+    <row r="81" ht="15.75" customHeight="1">
+      <c r="A81" s="48"/>
+      <c r="B81" s="74" t="s">
+        <v>99</v>
+      </c>
+      <c r="C81" s="73" t="s">
+        <v>25</v>
+      </c>
+      <c r="D81" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="E81" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F81" s="75"/>
+    </row>
+    <row r="82" ht="15.75" customHeight="1">
+      <c r="A82" s="48"/>
+      <c r="B82" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="C82" s="73" t="s">
+        <v>25</v>
+      </c>
+      <c r="D82" s="61" t="s">
+        <v>11</v>
+      </c>
+      <c r="E82" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F82" s="75"/>
+    </row>
+    <row r="83" ht="15.75" customHeight="1">
+      <c r="A83" s="48"/>
+      <c r="B83" s="74" t="s">
+        <v>101</v>
+      </c>
+      <c r="C83" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="D65" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E65" s="51"/>
-      <c r="F65" s="52"/>
-    </row>
-    <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="65"/>
-      <c r="B66" s="66" t="s">
-        <v>84</v>
-      </c>
-      <c r="C66" s="67" t="s">
+      <c r="D83" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="E83" s="46"/>
+      <c r="F83" s="75" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="84" ht="15.75" customHeight="1">
+      <c r="A84" s="48"/>
+      <c r="B84" s="74" t="s">
+        <v>103</v>
+      </c>
+      <c r="C84" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="D66" s="54" t="s">
-        <v>37</v>
-      </c>
-      <c r="E66" s="51"/>
-      <c r="F66" s="56" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="65"/>
-      <c r="B67" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="C67" s="68" t="s">
+      <c r="D84" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="E84" s="23"/>
+      <c r="F84" s="76"/>
+    </row>
+    <row r="85" ht="15.75" customHeight="1">
+      <c r="A85" s="48"/>
+      <c r="B85" s="74" t="s">
+        <v>104</v>
+      </c>
+      <c r="C85" s="73" t="s">
+        <v>25</v>
+      </c>
+      <c r="D85" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="E85" s="23"/>
+      <c r="F85" s="76"/>
+    </row>
+    <row r="86" ht="15.75" customHeight="1">
+      <c r="A86" s="48"/>
+      <c r="B86" s="74" t="s">
+        <v>105</v>
+      </c>
+      <c r="C86" s="73" t="s">
+        <v>25</v>
+      </c>
+      <c r="D86" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="E86" s="23"/>
+      <c r="F86" s="76"/>
+    </row>
+    <row r="87" ht="15.75" customHeight="1">
+      <c r="A87" s="48"/>
+      <c r="B87" s="77" t="s">
+        <v>106</v>
+      </c>
+      <c r="C87" s="73" t="s">
+        <v>25</v>
+      </c>
+      <c r="D87" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="E87" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F87" s="78"/>
+    </row>
+    <row r="88" ht="15.75" customHeight="1">
+      <c r="A88" s="48"/>
+      <c r="B88" s="79" t="s">
+        <v>107</v>
+      </c>
+      <c r="C88" s="80"/>
+      <c r="D88" s="80"/>
+      <c r="E88" s="80"/>
+      <c r="F88" s="81"/>
+    </row>
+    <row r="89" ht="15.75" customHeight="1">
+      <c r="A89" s="48"/>
+      <c r="B89" s="60" t="s">
+        <v>108</v>
+      </c>
+      <c r="C89" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="D67" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E67" s="51"/>
-      <c r="F67" s="52"/>
-    </row>
-    <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="65"/>
-      <c r="B68" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="C68" s="68" t="s">
+      <c r="D89" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E89" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F89" s="47"/>
+    </row>
+    <row r="90" ht="15.75" customHeight="1">
+      <c r="A90" s="48"/>
+      <c r="B90" s="60" t="s">
+        <v>109</v>
+      </c>
+      <c r="C90" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="D68" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E68" s="51" t="s">
+      <c r="D90" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E90" s="46"/>
+      <c r="F90" s="47"/>
+    </row>
+    <row r="91" ht="15.75" customHeight="1">
+      <c r="A91" s="48"/>
+      <c r="B91" s="60" t="s">
+        <v>110</v>
+      </c>
+      <c r="C91" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="D91" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="E91" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="F68" s="52"/>
-    </row>
-    <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="65"/>
-      <c r="B69" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="C69" s="68" t="s">
+      <c r="F91" s="63" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="92" ht="15.75" customHeight="1">
+      <c r="A92" s="48"/>
+      <c r="B92" s="60" t="s">
+        <v>112</v>
+      </c>
+      <c r="C92" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="D69" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E69" s="51" t="s">
+      <c r="D92" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E92" s="46"/>
+      <c r="F92" s="82"/>
+    </row>
+    <row r="93" ht="15.75" customHeight="1">
+      <c r="A93" s="48"/>
+      <c r="B93" s="60" t="s">
+        <v>113</v>
+      </c>
+      <c r="C93" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="D93" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E93" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="F69" s="52"/>
-    </row>
-    <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="65"/>
-      <c r="B70" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="C70" s="68" t="s">
+      <c r="F93" s="47"/>
+    </row>
+    <row r="94" ht="15.75" customHeight="1">
+      <c r="A94" s="48"/>
+      <c r="B94" s="71" t="s">
+        <v>114</v>
+      </c>
+      <c r="C94" s="72" t="s">
+        <v>25</v>
+      </c>
+      <c r="D94" s="83" t="s">
+        <v>11</v>
+      </c>
+      <c r="E94" s="83"/>
+      <c r="F94" s="84"/>
+    </row>
+    <row r="95" ht="15.75" customHeight="1">
+      <c r="A95" s="48"/>
+      <c r="B95" s="79" t="s">
+        <v>115</v>
+      </c>
+      <c r="C95" s="80"/>
+      <c r="D95" s="80"/>
+      <c r="E95" s="80"/>
+      <c r="F95" s="81"/>
+    </row>
+    <row r="96" ht="15.75" customHeight="1">
+      <c r="A96" s="48"/>
+      <c r="B96" s="85" t="s">
+        <v>116</v>
+      </c>
+      <c r="C96" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="D70" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E70" s="51" t="s">
+      <c r="D96" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E96" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="F70" s="52"/>
-    </row>
-    <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="65"/>
-      <c r="B71" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="C71" s="68" t="s">
+      <c r="F96" s="24"/>
+    </row>
+    <row r="97" ht="15.75" customHeight="1">
+      <c r="A97" s="48"/>
+      <c r="B97" s="86" t="s">
+        <v>117</v>
+      </c>
+      <c r="C97" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="D71" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E71" s="51" t="s">
+      <c r="D97" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E97" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="F71" s="52"/>
-    </row>
-    <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="65"/>
-      <c r="B72" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="C72" s="68" t="s">
+      <c r="F97" s="47"/>
+    </row>
+    <row r="98" ht="15.75" customHeight="1">
+      <c r="A98" s="48"/>
+      <c r="B98" s="60" t="s">
+        <v>118</v>
+      </c>
+      <c r="C98" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="D72" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E72" s="51" t="s">
+      <c r="D98" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E98" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="F72" s="52"/>
-    </row>
-    <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="65"/>
-      <c r="B73" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="C73" s="68" t="s">
+      <c r="F98" s="47"/>
+    </row>
+    <row r="99" ht="15.75" customHeight="1">
+      <c r="A99" s="48"/>
+      <c r="B99" s="60" t="s">
+        <v>119</v>
+      </c>
+      <c r="C99" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="D73" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E73" s="51"/>
-      <c r="F73" s="52"/>
-    </row>
-    <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="65"/>
-      <c r="B74" s="21" t="s">
-        <v>93</v>
-      </c>
-      <c r="C74" s="68" t="s">
+      <c r="D99" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E99" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F99" s="47"/>
+    </row>
+    <row r="100" ht="15.75" customHeight="1">
+      <c r="A100" s="48"/>
+      <c r="B100" s="60" t="s">
+        <v>120</v>
+      </c>
+      <c r="C100" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="D74" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E74" s="51" t="s">
+      <c r="D100" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E100" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="F74" s="52"/>
-    </row>
-    <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="65"/>
-      <c r="B75" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="C75" s="68" t="s">
+      <c r="F100" s="47"/>
+    </row>
+    <row r="101" ht="15.75" customHeight="1">
+      <c r="A101" s="48"/>
+      <c r="B101" s="60" t="s">
+        <v>121</v>
+      </c>
+      <c r="C101" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="D75" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E75" s="51" t="s">
+      <c r="D101" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E101" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="F75" s="52"/>
-    </row>
-    <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="65"/>
-      <c r="B76" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="C76" s="68" t="s">
+      <c r="F101" s="47"/>
+    </row>
+    <row r="102" ht="15.75" customHeight="1">
+      <c r="A102" s="48"/>
+      <c r="B102" s="60" t="s">
+        <v>122</v>
+      </c>
+      <c r="C102" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="D76" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E76" s="51" t="s">
+      <c r="D102" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E102" s="46"/>
+      <c r="F102" s="47"/>
+    </row>
+    <row r="103" ht="15.75" customHeight="1">
+      <c r="A103" s="48"/>
+      <c r="B103" s="60" t="s">
+        <v>123</v>
+      </c>
+      <c r="C103" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="D103" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E103" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="F76" s="52"/>
-    </row>
-    <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="65"/>
-      <c r="B77" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="C77" s="68" t="s">
+      <c r="F103" s="47"/>
+    </row>
+    <row r="104" ht="15.75" customHeight="1">
+      <c r="A104" s="48"/>
+      <c r="B104" s="60" t="s">
+        <v>124</v>
+      </c>
+      <c r="C104" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="D104" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E104" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F104" s="47"/>
+    </row>
+    <row r="105" ht="15.75" customHeight="1">
+      <c r="A105" s="48"/>
+      <c r="B105" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="C105" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="D105" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E105" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F105" s="47"/>
+    </row>
+    <row r="106" ht="15.75" customHeight="1">
+      <c r="A106" s="48"/>
+      <c r="B106" s="87" t="s">
+        <v>126</v>
+      </c>
+      <c r="C106" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="D77" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E77" s="51"/>
-      <c r="F77" s="52"/>
-    </row>
-    <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="65"/>
-      <c r="B78" s="69" t="s">
-        <v>97</v>
-      </c>
-      <c r="C78" s="68" t="s">
+      <c r="D106" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="E106" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F106" s="63" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="107" ht="15.75" customHeight="1">
+      <c r="A107" s="48"/>
+      <c r="B107" s="60" t="s">
+        <v>128</v>
+      </c>
+      <c r="C107" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="D78" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E78" s="51"/>
-      <c r="F78" s="52"/>
-    </row>
-    <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="65"/>
-      <c r="B79" s="69" t="s">
-        <v>98</v>
-      </c>
-      <c r="C79" s="68" t="s">
+      <c r="D107" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="E107" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F107" s="63" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="108" ht="15.75" customHeight="1">
+      <c r="A108" s="48"/>
+      <c r="B108" s="60" t="s">
+        <v>130</v>
+      </c>
+      <c r="C108" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="D108" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E108" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F108" s="47"/>
+    </row>
+    <row r="109" ht="15.75" customHeight="1">
+      <c r="A109" s="48"/>
+      <c r="B109" s="60" t="s">
+        <v>131</v>
+      </c>
+      <c r="C109" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="D109" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E109" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F109" s="47"/>
+    </row>
+    <row r="110" ht="15.75" customHeight="1">
+      <c r="A110" s="48"/>
+      <c r="B110" s="60" t="s">
+        <v>132</v>
+      </c>
+      <c r="C110" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="D110" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="E110" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F110" s="63" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="111" ht="15.75" customHeight="1">
+      <c r="A111" s="48"/>
+      <c r="B111" s="60" t="s">
+        <v>133</v>
+      </c>
+      <c r="C111" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="D79" s="54" t="s">
-        <v>37</v>
-      </c>
-      <c r="E79" s="51" t="s">
+      <c r="D111" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E111" s="46"/>
+      <c r="F111" s="47"/>
+    </row>
+    <row r="112" ht="15.75" customHeight="1">
+      <c r="A112" s="48"/>
+      <c r="B112" s="60" t="s">
+        <v>134</v>
+      </c>
+      <c r="C112" s="45" t="s">
+        <v>25</v>
+      </c>
+      <c r="D112" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E112" s="46"/>
+      <c r="F112" s="47"/>
+    </row>
+    <row r="113" ht="15.75" customHeight="1">
+      <c r="A113" s="48"/>
+      <c r="B113" s="60" t="s">
+        <v>135</v>
+      </c>
+      <c r="C113" s="45" t="s">
+        <v>25</v>
+      </c>
+      <c r="D113" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E113" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="F79" s="52"/>
-    </row>
-    <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="65"/>
-      <c r="B80" s="69" t="s">
-        <v>99</v>
-      </c>
-      <c r="C80" s="68" t="s">
-        <v>25</v>
-      </c>
-      <c r="D80" s="54" t="s">
-        <v>37</v>
-      </c>
-      <c r="E80" s="51" t="s">
+      <c r="F113" s="47"/>
+    </row>
+    <row r="114" ht="15.75" customHeight="1">
+      <c r="A114" s="48"/>
+      <c r="B114" s="64" t="s">
+        <v>136</v>
+      </c>
+      <c r="C114" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="D114" s="66" t="s">
+        <v>11</v>
+      </c>
+      <c r="E114" s="66"/>
+      <c r="F114" s="67"/>
+    </row>
+    <row r="115" ht="15.75" customHeight="1">
+      <c r="A115" s="59"/>
+      <c r="B115" s="68" t="s">
+        <v>137</v>
+      </c>
+      <c r="C115" s="69"/>
+      <c r="D115" s="69"/>
+      <c r="E115" s="69"/>
+      <c r="F115" s="70"/>
+    </row>
+    <row r="116" ht="15.75" customHeight="1">
+      <c r="A116" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="B116" s="88" t="s">
+        <v>139</v>
+      </c>
+      <c r="C116" s="89" t="s">
+        <v>10</v>
+      </c>
+      <c r="D116" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E116" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="F80" s="52"/>
-    </row>
-    <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="65"/>
-      <c r="B81" s="69" t="s">
-        <v>100</v>
-      </c>
-      <c r="C81" s="68" t="s">
-        <v>25</v>
-      </c>
-      <c r="D81" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="E81" s="51" t="s">
+      <c r="F116" s="24"/>
+    </row>
+    <row r="117" ht="15.75" customHeight="1">
+      <c r="A117" s="20"/>
+      <c r="B117" s="88" t="s">
+        <v>140</v>
+      </c>
+      <c r="C117" s="89" t="s">
+        <v>10</v>
+      </c>
+      <c r="D117" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E117" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="F81" s="52"/>
-    </row>
-    <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="65"/>
-      <c r="B82" s="69" t="s">
-        <v>101</v>
-      </c>
-      <c r="C82" s="68" t="s">
-        <v>25</v>
-      </c>
-      <c r="D82" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E82" s="51" t="s">
+      <c r="F117" s="24"/>
+    </row>
+    <row r="118" ht="15.75" customHeight="1">
+      <c r="A118" s="20"/>
+      <c r="B118" s="88" t="s">
+        <v>141</v>
+      </c>
+      <c r="C118" s="89" t="s">
+        <v>10</v>
+      </c>
+      <c r="D118" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E118" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="F82" s="70"/>
-    </row>
-    <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="65"/>
-      <c r="B83" s="69" t="s">
-        <v>102</v>
-      </c>
-      <c r="C83" s="68" t="s">
-        <v>25</v>
-      </c>
-      <c r="D83" s="54" t="s">
-        <v>37</v>
-      </c>
-      <c r="E83" s="51"/>
-      <c r="F83" s="70"/>
-    </row>
-    <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="65"/>
-      <c r="B84" s="69" t="s">
-        <v>103</v>
-      </c>
-      <c r="C84" s="68" t="s">
-        <v>25</v>
-      </c>
-      <c r="D84" s="54" t="s">
-        <v>37</v>
-      </c>
-      <c r="E84" s="51" t="s">
-        <v>12</v>
-      </c>
-      <c r="F84" s="70"/>
-    </row>
-    <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="65"/>
-      <c r="B85" s="69" t="s">
-        <v>104</v>
-      </c>
-      <c r="C85" s="68" t="s">
-        <v>25</v>
-      </c>
-      <c r="D85" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="E85" s="51" t="s">
-        <v>12</v>
-      </c>
-      <c r="F85" s="70"/>
-    </row>
-    <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="65"/>
-      <c r="B86" s="69" t="s">
-        <v>105</v>
-      </c>
-      <c r="C86" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="D86" s="54" t="s">
-        <v>37</v>
-      </c>
-      <c r="E86" s="51"/>
-      <c r="F86" s="70" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="65"/>
-      <c r="B87" s="69" t="s">
-        <v>107</v>
-      </c>
-      <c r="C87" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="D87" s="68" t="s">
-        <v>11</v>
-      </c>
-      <c r="E87" s="23"/>
-      <c r="F87" s="71"/>
-    </row>
-    <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="65"/>
-      <c r="B88" s="69" t="s">
-        <v>108</v>
-      </c>
-      <c r="C88" s="68" t="s">
-        <v>25</v>
-      </c>
-      <c r="D88" s="68" t="s">
-        <v>11</v>
-      </c>
-      <c r="E88" s="23"/>
-      <c r="F88" s="71"/>
-    </row>
-    <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="65"/>
-      <c r="B89" s="69" t="s">
-        <v>109</v>
-      </c>
-      <c r="C89" s="68" t="s">
-        <v>25</v>
-      </c>
-      <c r="D89" s="68" t="s">
-        <v>11</v>
-      </c>
-      <c r="E89" s="23"/>
-      <c r="F89" s="71"/>
-    </row>
-    <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="65"/>
-      <c r="B90" s="72" t="s">
-        <v>110</v>
-      </c>
-      <c r="C90" s="68" t="s">
-        <v>25</v>
-      </c>
-      <c r="D90" s="68" t="s">
-        <v>11</v>
-      </c>
-      <c r="E90" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="F90" s="73"/>
-    </row>
-    <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="65"/>
-      <c r="B91" s="74" t="s">
-        <v>111</v>
-      </c>
-      <c r="C91" s="75"/>
-      <c r="D91" s="75"/>
-      <c r="E91" s="75"/>
-      <c r="F91" s="76"/>
-    </row>
-    <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="65"/>
-      <c r="B92" s="49" t="s">
-        <v>112</v>
-      </c>
-      <c r="C92" s="50" t="s">
-        <v>10</v>
-      </c>
-      <c r="D92" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E92" s="51" t="s">
-        <v>12</v>
-      </c>
-      <c r="F92" s="52"/>
-    </row>
-    <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="65"/>
-      <c r="B93" s="49" t="s">
-        <v>113</v>
-      </c>
-      <c r="C93" s="50" t="s">
-        <v>10</v>
-      </c>
-      <c r="D93" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E93" s="51"/>
-      <c r="F93" s="52"/>
-    </row>
-    <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="65"/>
-      <c r="B94" s="49" t="s">
-        <v>114</v>
-      </c>
-      <c r="C94" s="50" t="s">
-        <v>10</v>
-      </c>
-      <c r="D94" s="54" t="s">
-        <v>37</v>
-      </c>
-      <c r="E94" s="51" t="s">
-        <v>12</v>
-      </c>
-      <c r="F94" s="56" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="65"/>
-      <c r="B95" s="49" t="s">
-        <v>116</v>
-      </c>
-      <c r="C95" s="50" t="s">
-        <v>10</v>
-      </c>
-      <c r="D95" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E95" s="51"/>
-      <c r="F95" s="77"/>
-    </row>
-    <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="65"/>
-      <c r="B96" s="49" t="s">
-        <v>117</v>
-      </c>
-      <c r="C96" s="50" t="s">
-        <v>10</v>
-      </c>
-      <c r="D96" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E96" s="51" t="s">
-        <v>12</v>
-      </c>
-      <c r="F96" s="52"/>
-    </row>
-    <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="65"/>
-      <c r="B97" s="66" t="s">
-        <v>118</v>
-      </c>
-      <c r="C97" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="D97" s="78" t="s">
-        <v>11</v>
-      </c>
-      <c r="E97" s="78"/>
-      <c r="F97" s="79"/>
-    </row>
-    <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="65"/>
-      <c r="B98" s="74" t="s">
-        <v>119</v>
-      </c>
-      <c r="C98" s="75"/>
-      <c r="D98" s="75"/>
-      <c r="E98" s="75"/>
-      <c r="F98" s="76"/>
-    </row>
-    <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="65"/>
-      <c r="B99" s="80" t="s">
-        <v>120</v>
-      </c>
-      <c r="C99" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="D99" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="E99" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="F99" s="24"/>
-    </row>
-    <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="65"/>
-      <c r="B100" s="81" t="s">
-        <v>121</v>
-      </c>
-      <c r="C100" s="50" t="s">
-        <v>10</v>
-      </c>
-      <c r="D100" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E100" s="51" t="s">
-        <v>12</v>
-      </c>
-      <c r="F100" s="52"/>
-    </row>
-    <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="65"/>
-      <c r="B101" s="49" t="s">
-        <v>122</v>
-      </c>
-      <c r="C101" s="50" t="s">
-        <v>10</v>
-      </c>
-      <c r="D101" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E101" s="51" t="s">
-        <v>12</v>
-      </c>
-      <c r="F101" s="52"/>
-    </row>
-    <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="65"/>
-      <c r="B102" s="49" t="s">
-        <v>123</v>
-      </c>
-      <c r="C102" s="50" t="s">
-        <v>10</v>
-      </c>
-      <c r="D102" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E102" s="51" t="s">
-        <v>12</v>
-      </c>
-      <c r="F102" s="52"/>
-    </row>
-    <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="65"/>
-      <c r="B103" s="49" t="s">
-        <v>124</v>
-      </c>
-      <c r="C103" s="50" t="s">
-        <v>10</v>
-      </c>
-      <c r="D103" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E103" s="51" t="s">
-        <v>12</v>
-      </c>
-      <c r="F103" s="52"/>
-    </row>
-    <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="65"/>
-      <c r="B104" s="49" t="s">
-        <v>125</v>
-      </c>
-      <c r="C104" s="50" t="s">
-        <v>10</v>
-      </c>
-      <c r="D104" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E104" s="51" t="s">
-        <v>12</v>
-      </c>
-      <c r="F104" s="52"/>
-    </row>
-    <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="65"/>
-      <c r="B105" s="49" t="s">
-        <v>126</v>
-      </c>
-      <c r="C105" s="50" t="s">
-        <v>10</v>
-      </c>
-      <c r="D105" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E105" s="51"/>
-      <c r="F105" s="52"/>
-    </row>
-    <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="65"/>
-      <c r="B106" s="49" t="s">
-        <v>127</v>
-      </c>
-      <c r="C106" s="50" t="s">
-        <v>10</v>
-      </c>
-      <c r="D106" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E106" s="51" t="s">
-        <v>12</v>
-      </c>
-      <c r="F106" s="52"/>
-    </row>
-    <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="65"/>
-      <c r="B107" s="49" t="s">
-        <v>128</v>
-      </c>
-      <c r="C107" s="50" t="s">
-        <v>10</v>
-      </c>
-      <c r="D107" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E107" s="51" t="s">
-        <v>12</v>
-      </c>
-      <c r="F107" s="52"/>
-    </row>
-    <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="65"/>
-      <c r="B108" s="49" t="s">
-        <v>129</v>
-      </c>
-      <c r="C108" s="50" t="s">
-        <v>10</v>
-      </c>
-      <c r="D108" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E108" s="51" t="s">
-        <v>12</v>
-      </c>
-      <c r="F108" s="52"/>
-    </row>
-    <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="65"/>
-      <c r="B109" s="82" t="s">
-        <v>130</v>
-      </c>
-      <c r="C109" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="D109" s="54" t="s">
-        <v>37</v>
-      </c>
-      <c r="E109" s="51" t="s">
-        <v>12</v>
-      </c>
-      <c r="F109" s="56" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="65"/>
-      <c r="B110" s="49" t="s">
-        <v>132</v>
-      </c>
-      <c r="C110" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="D110" s="54" t="s">
-        <v>37</v>
-      </c>
-      <c r="E110" s="51" t="s">
-        <v>12</v>
-      </c>
-      <c r="F110" s="56" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="65"/>
-      <c r="B111" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="C111" s="50" t="s">
-        <v>10</v>
-      </c>
-      <c r="D111" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E111" s="51" t="s">
-        <v>12</v>
-      </c>
-      <c r="F111" s="52"/>
-    </row>
-    <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="65"/>
-      <c r="B112" s="49" t="s">
-        <v>135</v>
-      </c>
-      <c r="C112" s="50" t="s">
-        <v>10</v>
-      </c>
-      <c r="D112" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E112" s="51" t="s">
-        <v>12</v>
-      </c>
-      <c r="F112" s="52"/>
-    </row>
-    <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="65"/>
-      <c r="B113" s="49" t="s">
-        <v>136</v>
-      </c>
-      <c r="C113" s="50" t="s">
-        <v>10</v>
-      </c>
-      <c r="D113" s="54" t="s">
-        <v>37</v>
-      </c>
-      <c r="E113" s="51" t="s">
-        <v>12</v>
-      </c>
-      <c r="F113" s="56" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="65"/>
-      <c r="B114" s="49" t="s">
-        <v>137</v>
-      </c>
-      <c r="C114" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="D114" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E114" s="51"/>
-      <c r="F114" s="52"/>
-    </row>
-    <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="65"/>
-      <c r="B115" s="49" t="s">
-        <v>138</v>
-      </c>
-      <c r="C115" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="D115" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E115" s="51"/>
-      <c r="F115" s="52"/>
-    </row>
-    <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="65"/>
-      <c r="B116" s="49" t="s">
-        <v>139</v>
-      </c>
-      <c r="C116" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="D116" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E116" s="51" t="s">
-        <v>12</v>
-      </c>
-      <c r="F116" s="52"/>
-    </row>
-    <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="83"/>
-      <c r="B117" s="57" t="s">
-        <v>140</v>
-      </c>
-      <c r="C117" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="D117" s="59" t="s">
-        <v>11</v>
-      </c>
-      <c r="E117" s="59"/>
-      <c r="F117" s="60"/>
-    </row>
-    <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="B118" s="62" t="s">
-        <v>142</v>
-      </c>
-      <c r="C118" s="63"/>
-      <c r="D118" s="63"/>
-      <c r="E118" s="63"/>
-      <c r="F118" s="64"/>
+      <c r="F118" s="24"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="20"/>
-      <c r="B119" s="84" t="s">
-        <v>143</v>
-      </c>
-      <c r="C119" s="85" t="s">
+      <c r="B119" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="C119" s="22" t="s">
         <v>10</v>
       </c>
       <c r="D119" s="23" t="s">
@@ -3295,10 +3307,10 @@
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="20"/>
-      <c r="B120" s="84" t="s">
-        <v>144</v>
-      </c>
-      <c r="C120" s="85" t="s">
+      <c r="B120" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="C120" s="22" t="s">
         <v>10</v>
       </c>
       <c r="D120" s="23" t="s">
@@ -3311,42 +3323,36 @@
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="20"/>
-      <c r="B121" s="84" t="s">
-        <v>145</v>
-      </c>
-      <c r="C121" s="85" t="s">
+      <c r="B121" s="90" t="s">
+        <v>144</v>
+      </c>
+      <c r="C121" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="D121" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="E121" s="23" t="s">
+      <c r="D121" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E121" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="F121" s="24"/>
+      <c r="F121" s="34"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="20"/>
-      <c r="B122" s="21" t="s">
+      <c r="B122" s="91" t="s">
+        <v>145</v>
+      </c>
+      <c r="C122" s="92"/>
+      <c r="D122" s="92"/>
+      <c r="E122" s="92"/>
+      <c r="F122" s="93"/>
+    </row>
+    <row r="123" ht="24.0" customHeight="1">
+      <c r="A123" s="20"/>
+      <c r="B123" s="60" t="s">
         <v>146</v>
       </c>
-      <c r="C122" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="D122" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="E122" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="F122" s="24"/>
-    </row>
-    <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="20"/>
-      <c r="B123" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="C123" s="22" t="s">
+      <c r="C123" s="45" t="s">
         <v>10</v>
       </c>
       <c r="D123" s="23" t="s">
@@ -3360,7 +3366,7 @@
     <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="20"/>
       <c r="B124" s="21" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C124" s="22" t="s">
         <v>10</v>
@@ -3373,23 +3379,29 @@
       </c>
       <c r="F124" s="24"/>
     </row>
-    <row r="125" ht="24.0" customHeight="1">
+    <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="20"/>
-      <c r="B125" s="86" t="s">
-        <v>149</v>
-      </c>
-      <c r="C125" s="87"/>
-      <c r="D125" s="87"/>
-      <c r="E125" s="87"/>
-      <c r="F125" s="88"/>
+      <c r="B125" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="C125" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="D125" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E125" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F125" s="24"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="20"/>
-      <c r="B126" s="49" t="s">
-        <v>150</v>
-      </c>
-      <c r="C126" s="50" t="s">
-        <v>10</v>
+      <c r="B126" s="90" t="s">
+        <v>149</v>
+      </c>
+      <c r="C126" s="32" t="s">
+        <v>25</v>
       </c>
       <c r="D126" s="23" t="s">
         <v>11</v>
@@ -3402,10 +3414,10 @@
     <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="20"/>
       <c r="B127" s="21" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C127" s="22" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D127" s="23" t="s">
         <v>11</v>
@@ -3418,7 +3430,7 @@
     <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="20"/>
       <c r="B128" s="21" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C128" s="22" t="s">
         <v>25</v>
@@ -3433,40 +3445,34 @@
     </row>
     <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="20"/>
-      <c r="B129" s="89" t="s">
-        <v>153</v>
-      </c>
-      <c r="C129" s="32" t="s">
-        <v>25</v>
-      </c>
-      <c r="D129" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="E129" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="F129" s="24"/>
+      <c r="B129" s="94" t="s">
+        <v>152</v>
+      </c>
+      <c r="C129" s="95"/>
+      <c r="D129" s="95"/>
+      <c r="E129" s="95"/>
+      <c r="F129" s="96"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="20"/>
-      <c r="B130" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="C130" s="22" t="s">
+      <c r="B130" s="60" t="s">
+        <v>153</v>
+      </c>
+      <c r="C130" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="D130" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="E130" s="23" t="s">
+      <c r="D130" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E130" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="F130" s="24"/>
+      <c r="F130" s="47"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="20"/>
       <c r="B131" s="21" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C131" s="22" t="s">
         <v>25</v>
@@ -3481,18 +3487,24 @@
     </row>
     <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="20"/>
-      <c r="B132" s="90" t="s">
-        <v>156</v>
-      </c>
-      <c r="C132" s="91"/>
-      <c r="D132" s="91"/>
-      <c r="E132" s="91"/>
-      <c r="F132" s="92"/>
+      <c r="B132" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="C132" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="D132" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E132" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F132" s="24"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="20"/>
       <c r="B133" s="21" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C133" s="22" t="s">
         <v>25</v>
@@ -3508,18 +3520,20 @@
     <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="20"/>
       <c r="B134" s="21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C134" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="D134" s="23" t="s">
-        <v>11</v>
+      <c r="D134" s="38" t="s">
+        <v>36</v>
       </c>
       <c r="E134" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="F134" s="24"/>
+      <c r="F134" s="50" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="20"/>
@@ -3543,7 +3557,7 @@
         <v>160</v>
       </c>
       <c r="C136" s="22" t="s">
-        <v>25</v>
+        <v>161</v>
       </c>
       <c r="D136" s="23" t="s">
         <v>11</v>
@@ -3556,20 +3570,18 @@
     <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="20"/>
       <c r="B137" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="C137" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="C137" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="D137" s="38" t="s">
-        <v>37</v>
+      <c r="D137" s="23" t="s">
+        <v>11</v>
       </c>
       <c r="E137" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="F137" s="43" t="s">
-        <v>162</v>
-      </c>
+      <c r="F137" s="24"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="20"/>
@@ -3589,43 +3601,45 @@
     </row>
     <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="20"/>
-      <c r="B139" s="21" t="s">
+      <c r="B139" s="97" t="s">
         <v>164</v>
       </c>
-      <c r="C139" s="22" t="s">
+      <c r="C139" s="98" t="s">
+        <v>161</v>
+      </c>
+      <c r="D139" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E139" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="F139" s="28"/>
+    </row>
+    <row r="140" ht="15.75" customHeight="1">
+      <c r="A140" s="10"/>
+      <c r="B140" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="D139" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="E139" s="23" t="s">
+      <c r="C140" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D140" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E140" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F139" s="24"/>
-    </row>
-    <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="20"/>
-      <c r="B140" s="21" t="s">
+      <c r="F140" s="19"/>
+    </row>
+    <row r="141" ht="15.75" customHeight="1">
+      <c r="A141" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="C140" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="D140" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="E140" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="F140" s="24"/>
-    </row>
-    <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="20"/>
       <c r="B141" s="21" t="s">
         <v>167</v>
       </c>
       <c r="C141" s="22" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D141" s="23" t="s">
         <v>11</v>
@@ -3636,43 +3650,41 @@
       <c r="F141" s="24"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="10"/>
-      <c r="B142" s="93" t="s">
+      <c r="A142" s="20"/>
+      <c r="B142" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="C142" s="94" t="s">
-        <v>165</v>
-      </c>
-      <c r="D142" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="E142" s="27" t="s">
+      <c r="C142" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D142" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E142" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="F142" s="28"/>
+      <c r="F142" s="24"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="15" t="s">
+      <c r="A143" s="20"/>
+      <c r="B143" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="B143" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="C143" s="17" t="s">
+      <c r="C143" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="D143" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="E143" s="18" t="s">
+      <c r="D143" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E143" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="F143" s="19"/>
+      <c r="F143" s="24"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="20"/>
       <c r="B144" s="21" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C144" s="22" t="s">
         <v>10</v>
@@ -3688,7 +3700,7 @@
     <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="20"/>
       <c r="B145" s="21" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C145" s="22" t="s">
         <v>10</v>
@@ -3703,85 +3715,58 @@
     </row>
     <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="20"/>
-      <c r="B146" s="21" t="s">
+      <c r="B146" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="C146" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D146" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E146" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="F146" s="28"/>
+    </row>
+    <row r="147" ht="15.75" customHeight="1">
+      <c r="A147" s="10"/>
+      <c r="B147" s="64" t="s">
         <v>173</v>
       </c>
-      <c r="C146" s="22" t="s">
+      <c r="C147" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="D146" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="E146" s="23" t="s">
+      <c r="D147" s="99" t="s">
+        <v>36</v>
+      </c>
+      <c r="E147" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="F146" s="24"/>
-    </row>
-    <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="20"/>
-      <c r="B147" s="21" t="s">
+      <c r="F147" s="67"/>
+    </row>
+    <row r="148" ht="15.75" customHeight="1">
+      <c r="A148" s="100" t="s">
         <v>174</v>
       </c>
-      <c r="C147" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="D147" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="E147" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="F147" s="24"/>
-    </row>
-    <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="20"/>
-      <c r="B148" s="21" t="s">
-        <v>175</v>
-      </c>
-      <c r="C148" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="D148" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="E148" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="F148" s="24"/>
+      <c r="B148" s="2"/>
+      <c r="C148" s="1"/>
+      <c r="D148" s="1"/>
+      <c r="E148" s="1"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="10"/>
-      <c r="B149" s="25" t="s">
-        <v>176</v>
-      </c>
-      <c r="C149" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="D149" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="E149" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="F149" s="28"/>
+      <c r="A149" s="1"/>
+      <c r="B149" s="2"/>
+      <c r="C149" s="1"/>
+      <c r="D149" s="1"/>
+      <c r="E149" s="1"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="95" t="s">
-        <v>177</v>
-      </c>
-      <c r="B150" s="57" t="s">
-        <v>178</v>
-      </c>
-      <c r="C150" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="D150" s="96" t="s">
-        <v>37</v>
-      </c>
-      <c r="E150" s="59" t="s">
-        <v>12</v>
-      </c>
-      <c r="F150" s="60"/>
+      <c r="A150" s="1"/>
+      <c r="B150" s="2"/>
+      <c r="C150" s="1"/>
+      <c r="D150" s="1"/>
+      <c r="E150" s="1"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="1"/>
@@ -9714,43 +9699,25 @@
     </row>
     <row r="998" ht="15.75" customHeight="1">
       <c r="A998" s="1"/>
-      <c r="B998" s="2"/>
-      <c r="C998" s="1"/>
-      <c r="D998" s="1"/>
-      <c r="E998" s="1"/>
-    </row>
-    <row r="999" ht="15.75" customHeight="1">
-      <c r="A999" s="1"/>
-      <c r="B999" s="2"/>
-      <c r="C999" s="1"/>
-      <c r="D999" s="1"/>
-      <c r="E999" s="1"/>
-    </row>
-    <row r="1000" ht="15.75" customHeight="1">
-      <c r="A1000" s="1"/>
-      <c r="B1000" s="2"/>
-      <c r="C1000" s="1"/>
-      <c r="D1000" s="1"/>
-      <c r="E1000" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A23:A27"/>
-    <mergeCell ref="A28:A30"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="A35:A44"/>
-    <mergeCell ref="A45:A63"/>
-    <mergeCell ref="A64:A117"/>
-    <mergeCell ref="A118:A142"/>
-    <mergeCell ref="A143:A149"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B91:F91"/>
-    <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B125:F125"/>
-    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A43:A61"/>
+    <mergeCell ref="A62:A115"/>
+    <mergeCell ref="A116:A140"/>
+    <mergeCell ref="A141:A147"/>
+    <mergeCell ref="A34:A42"/>
+    <mergeCell ref="A23:A26"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="B88:F88"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B122:F122"/>
+    <mergeCell ref="B129:F129"/>
     <mergeCell ref="A2:F3"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
@@ -9760,7 +9727,7 @@
     <mergeCell ref="A7:A22"/>
   </mergeCells>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="C7:C34 C36:C39 C41:C63 C65:C90 C92:C97 C99:C117 C122:C124 C126:C131 C133:C141 C143:C150">
+    <dataValidation type="list" allowBlank="1" sqref="C7:C32 C34:C36 C38:C60 C62:C87 C89:C94 C96:C114 C119:C121 C123:C128 C130:C138 C140:C147">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>
